--- a/DATA_KELULUSAN_KELAS_XII_2026.xlsx
+++ b/DATA_KELULUSAN_KELAS_XII_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kaka\Web_Sekolah\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679C19E9-585B-4FA1-A03E-0D14A729E4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E40DCC-B613-4412-A8FD-E5D8C1AA5B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{727BADB8-D875-40A7-BFF0-F28165CFFF77}"/>
   </bookViews>

--- a/DATA_KELULUSAN_KELAS_XII_2026.xlsx
+++ b/DATA_KELULUSAN_KELAS_XII_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kaka\Web_Sekolah\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E40DCC-B613-4412-A8FD-E5D8C1AA5B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB64819-AB74-4431-A779-15BF4555EC06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{727BADB8-D875-40A7-BFF0-F28165CFFF77}"/>
   </bookViews>
